--- a/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/unbedenklichkeitsbescheinigungen_status.xlsx
+++ b/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/unbedenklichkeitsbescheinigungen_status.xlsx
@@ -71,6 +71,21 @@
           <t>confidence</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>source_snippet</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>matched_pattern</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>extraction_method</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -133,6 +148,21 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>vorgenannten Betriebsnummer geführten Arbeitgeberkonto, derzeit keine Beitragsrückstände</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>unbedenklichkeitsbescheinigung</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>certificate_status_text</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -195,6 +225,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>unbedenklichkeitsbescheinigung</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>certificate_status_text</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -255,6 +300,21 @@
       <c r="L4" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>nachgewiesen und gezahlt worden sind und derzeit keine Beitragsrückstände bestehen.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>unbedenklichkeitsbescheinigung</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>certificate_status_text</t>
         </is>
       </c>
     </row>
